--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_2B59D18754BA3E647B79371159A1B0F24E23FF46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68F3C1F2-941B-41BD-B84A-E96347616DED}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_2B59D18754BA3E647B79371159A1B0F24E23FF46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8E9965F-B8DA-4E0F-B9EA-DC38B3EC63EC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
   <si>
     <t>Data</t>
   </si>
@@ -129,15 +129,6 @@
   </si>
   <si>
     <t>Afturelding x Grotta</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>COPA LIBERTADORES</t>
-  </si>
-  <si>
-    <t>Independiente (Ecu) x Tolima</t>
   </si>
   <si>
     <t>1/0</t>
@@ -524,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
@@ -565,10 +556,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -651,7 +642,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M7" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
+        <f t="shared" ref="M3:M6" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
         <v>0.25130208333333331</v>
       </c>
     </row>
@@ -779,48 +770,6 @@
       <c r="M6">
         <f t="shared" si="0"/>
         <v>0.14577039274924469</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>11.55</v>
-      </c>
-      <c r="I7">
-        <v>1.57</v>
-      </c>
-      <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="0"/>
-        <v>9.1469194312796195E-2</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
@@ -224,10 +224,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
